--- a/inputs/stage2_sample_absolute_setpoints.xlsx
+++ b/inputs/stage2_sample_absolute_setpoints.xlsx
@@ -128,20 +128,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,813 +334,808 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C73"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.82"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>44569.2916666667</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>44569.3020833333</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>44569.3125</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>32</v>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="A5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>44569.3229166667</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>11</v>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="n">
+      <c r="A6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>44569.3333333333</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="A7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>44569.34375</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>11</v>
+      <c r="C7" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="n">
+      <c r="A8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>44569.3541666667</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="n">
+      <c r="A9" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>44569.3645833333</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>11</v>
+      <c r="C9" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="3" t="n">
+      <c r="A10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>44569.375</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3" t="n">
+      <c r="A11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>44569.3854166667</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>16.5</v>
+      <c r="C11" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="3" t="n">
+      <c r="A12" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>44569.3958333333</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>11</v>
+      <c r="C12" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="3" t="n">
+      <c r="A13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>44569.40625</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="n">
+      <c r="A14" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>44569.4166666667</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="n">
+      <c r="A15" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>44569.4270833333</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>5.5</v>
+      <c r="C15" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="3" t="n">
+      <c r="A16" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>44569.4375</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>11</v>
+      <c r="C16" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="3" t="n">
+      <c r="A17" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>44569.4479166667</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>11</v>
+      <c r="C17" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3" t="n">
+      <c r="A18" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>44569.4583333333</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>11</v>
+      <c r="C18" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="3" t="n">
+      <c r="A19" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>44569.46875</v>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>5.5</v>
+      <c r="C19" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="3" t="n">
+      <c r="A20" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>44569.4791666667</v>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>5.5</v>
+      <c r="C20" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="3" t="n">
+      <c r="A21" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="n">
         <v>44569.4895833333</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="n">
+      <c r="A22" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2" t="n">
         <v>44569.5</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="3" t="n">
+      <c r="A23" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="n">
         <v>44569.5104166667</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="3" t="n">
+      <c r="A24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="n">
         <v>44569.5208333333</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="3" t="n">
+      <c r="A25" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>44569.53125</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="3" t="n">
+      <c r="A26" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>44569.2916666667</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="3" t="n">
+      <c r="A27" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>44569.3020833333</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="3" t="n">
+      <c r="A28" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>44569.3125</v>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>5.5</v>
+      <c r="C28" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="3" t="n">
+      <c r="A29" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>44569.3229166667</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="3" t="n">
+      <c r="A30" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>44569.3333333333</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="3" t="n">
+      <c r="A31" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>44569.34375</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="3" t="n">
+      <c r="A32" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2" t="n">
         <v>44569.3541666667</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="3" t="n">
+      <c r="A33" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2" t="n">
         <v>44569.3645833333</v>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>16.5</v>
+      <c r="C33" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="3" t="n">
+      <c r="A34" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>44569.375</v>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>16.5</v>
+      <c r="C34" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="3" t="n">
+      <c r="A35" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>44569.3854166667</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="3" t="n">
+      <c r="A36" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>44569.3958333333</v>
       </c>
-      <c r="C36" s="1" t="n">
-        <v>5.5</v>
+      <c r="C36" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="3" t="n">
+      <c r="A37" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>44569.40625</v>
       </c>
-      <c r="C37" s="1" t="n">
-        <v>5.5</v>
+      <c r="C37" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="3" t="n">
+      <c r="A38" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>44569.4166666667</v>
       </c>
-      <c r="C38" s="1" t="n">
-        <v>16.5</v>
+      <c r="C38" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="3" t="n">
+      <c r="A39" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>44569.4270833333</v>
       </c>
-      <c r="C39" s="1" t="n">
-        <v>16.5</v>
+      <c r="C39" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="3" t="n">
+      <c r="A40" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>44569.4375</v>
       </c>
-      <c r="C40" s="1" t="n">
-        <v>16.5</v>
+      <c r="C40" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="3" t="n">
+      <c r="A41" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="2" t="n">
         <v>44569.4479166667</v>
       </c>
-      <c r="C41" s="1" t="n">
-        <v>16.5</v>
+      <c r="C41" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="3" t="n">
+      <c r="A42" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="2" t="n">
         <v>44569.4583333333</v>
       </c>
-      <c r="C42" s="1" t="n">
-        <v>11</v>
+      <c r="C42" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="3" t="n">
+      <c r="A43" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="2" t="n">
         <v>44569.46875</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="3" t="n">
+      <c r="A44" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>44569.4791666667</v>
       </c>
-      <c r="C44" s="1" t="n">
-        <v>5.5</v>
+      <c r="C44" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="3" t="n">
+      <c r="A45" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="2" t="n">
         <v>44569.4895833333</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="3" t="n">
+      <c r="A46" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>44569.5</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="3" t="n">
+      <c r="A47" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="2" t="n">
         <v>44569.5104166667</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="3" t="n">
+      <c r="A48" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>44569.5208333333</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="3" t="n">
+      <c r="A49" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>44569.53125</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="3" t="n">
+      <c r="A50" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>44569.2916666667</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="3" t="n">
+      <c r="A51" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>44569.3020833333</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B52" s="3" t="n">
+      <c r="A52" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="2" t="n">
         <v>44569.3125</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="3" t="n">
+      <c r="A53" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="2" t="n">
         <v>44569.3229166667</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B54" s="3" t="n">
+      <c r="A54" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="2" t="n">
         <v>44569.3333333333</v>
       </c>
-      <c r="C54" s="1" t="n">
-        <v>5.5</v>
+      <c r="C54" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B55" s="3" t="n">
+      <c r="A55" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="2" t="n">
         <v>44569.34375</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" s="3" t="n">
+      <c r="A56" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>44569.3541666667</v>
       </c>
-      <c r="C56" s="1" t="n">
-        <v>11</v>
+      <c r="C56" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B57" s="3" t="n">
+      <c r="A57" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="2" t="n">
         <v>44569.3645833333</v>
       </c>
-      <c r="C57" s="1" t="n">
-        <v>16.5</v>
+      <c r="C57" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" s="3" t="n">
+      <c r="A58" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="2" t="n">
         <v>44569.375</v>
       </c>
-      <c r="C58" s="1" t="n">
-        <v>11</v>
+      <c r="C58" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" s="3" t="n">
+      <c r="A59" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="2" t="n">
         <v>44569.3854166667</v>
       </c>
-      <c r="C59" s="1" t="n">
-        <v>5.5</v>
+      <c r="C59" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60" s="3" t="n">
+      <c r="A60" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="2" t="n">
         <v>44569.3958333333</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61" s="3" t="n">
+      <c r="A61" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="2" t="n">
         <v>44569.40625</v>
       </c>
-      <c r="C61" s="1" t="n">
-        <v>16.5</v>
+      <c r="C61" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B62" s="3" t="n">
+      <c r="A62" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="2" t="n">
         <v>44569.4166666667</v>
       </c>
-      <c r="C62" s="1" t="n">
-        <v>16.5</v>
+      <c r="C62" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B63" s="3" t="n">
+      <c r="A63" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="2" t="n">
         <v>44569.4270833333</v>
       </c>
-      <c r="C63" s="1" t="n">
-        <v>5.5</v>
+      <c r="C63" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B64" s="3" t="n">
+      <c r="A64" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="2" t="n">
         <v>44569.4375</v>
       </c>
-      <c r="C64" s="1" t="n">
-        <v>16.5</v>
+      <c r="C64" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B65" s="3" t="n">
+      <c r="A65" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="2" t="n">
         <v>44569.4479166667</v>
       </c>
-      <c r="C65" s="1" t="n">
-        <v>16.5</v>
+      <c r="C65" s="0" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B66" s="3" t="n">
+      <c r="A66" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="2" t="n">
         <v>44569.4583333333</v>
       </c>
-      <c r="C66" s="1" t="n">
-        <v>16.5</v>
+      <c r="C66" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B67" s="3" t="n">
+      <c r="A67" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="2" t="n">
         <v>44569.46875</v>
       </c>
-      <c r="C67" s="1" t="n">
-        <v>5.5</v>
+      <c r="C67" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68" s="3" t="n">
+      <c r="A68" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="2" t="n">
         <v>44569.4791666667</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69" s="3" t="n">
+      <c r="A69" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="2" t="n">
         <v>44569.4895833333</v>
       </c>
-      <c r="C69" s="1" t="n">
-        <v>5.5</v>
+      <c r="C69" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B70" s="3" t="n">
+      <c r="A70" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="2" t="n">
         <v>44569.5</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B71" s="3" t="n">
+      <c r="A71" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="2" t="n">
         <v>44569.5104166667</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B72" s="3" t="n">
+      <c r="A72" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="2" t="n">
         <v>44569.5208333333</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B73" s="3" t="n">
+      <c r="A73" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="2" t="n">
         <v>44569.53125</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="0" t="n">
         <v>0</v>
       </c>
     </row>
